--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>اسامة احمد جمال هلالي</v>
+        <v>مزمل عوض طه احمد</v>
       </c>
       <c r="C11" t="str">
         <v>114</v>
@@ -621,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>اكرم محمدعثمان ميراحمد طاشكندي</v>
+        <v>ياسين مصطفي محمود شمس</v>
       </c>
       <c r="C12" t="str">
         <v>مبنى 5000 - مكتب 5113</v>
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>عبد الرحمن عبد الله عبد الرحمن عبد الله</v>
+        <v>د. عبدالرحمن عبدالله</v>
       </c>
       <c r="C15" t="str">
         <v>112</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>د. عبدالرحمن عبدالله</v>
+        <v>عبد الرحمن عبد الله عبد الرحمن عبد الله</v>
       </c>
       <c r="C15" t="str">
         <v>112</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/المحاسبة_طلاب.xlsx
@@ -464,7 +464,7 @@
         <v>اكرم محمدعثمان ميراحمد طاشكندي</v>
       </c>
       <c r="C4" t="str">
-        <v>مبنى 5000 - مكتب 5113</v>
+        <v>5113</v>
       </c>
       <c r="D4" t="str">
         <v>الفترة الأولى</v>
@@ -504,7 +504,7 @@
         <v>عدنان يعقوب علي عاشق</v>
       </c>
       <c r="C6" t="str">
-        <v>مبنى 5000 - مكتب 114</v>
+        <v>114</v>
       </c>
       <c r="D6" t="str">
         <v>الفترة الأولى</v>
@@ -624,7 +624,7 @@
         <v>ياسين مصطفي محمود شمس</v>
       </c>
       <c r="C12" t="str">
-        <v>مبنى 5000 - مكتب 5113</v>
+        <v>5113</v>
       </c>
       <c r="D12" t="str">
         <v>الفترة الثانية</v>
